--- a/output/reporte_cobertura_controlsano_0a6_RM_2025.xlsx
+++ b/output/reporte_cobertura_controlsano_0a6_RM_2025.xlsx
@@ -498,7 +498,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>'Bajo control' = al día + inasistentes dentro del plazo (siguen en P2 A/A.1). P2 se informa en junio y diciembre; se usa diciembre.</t>
+          <t>'Bajo control' = al día + inasistentes dentro del plazo (siguen en P2 A/A.1). P2 es stock semestral (jun/dic): se usa SOLO diciembre, no se suman.</t>
         </is>
       </c>
     </row>

--- a/output/reporte_cobertura_controlsano_0a6_RM_2025.xlsx
+++ b/output/reporte_cobertura_controlsano_0a6_RM_2025.xlsx
@@ -11462,7 +11462,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">

--- a/output/reporte_cobertura_controlsano_0a6_RM_2025.xlsx
+++ b/output/reporte_cobertura_controlsano_0a6_RM_2025.xlsx
@@ -526,7 +526,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Advertencia: coberturas &gt;100% en centros/comunas pequeñas ocurren porque el numerador cuenta donde se atiende y el denominador donde se inscribe (ej. CECOSF, postas). San José de Maipo trae denominador incompleto en T8009 (solo 1 posta); verificar con FONASA antes de responder.</t>
+          <t>Advertencia: coberturas &gt;100% en centros/comunas pequeñas ocurren porque el numerador cuenta donde se atiende y el denominador donde se inscribe (ej. CECOSF, postas).</t>
         </is>
       </c>
     </row>
